--- a/04_Kernel_Functions/data/datos_sinteticos_polinomial.xlsx
+++ b/04_Kernel_Functions/data/datos_sinteticos_polinomial.xlsx
@@ -469,10 +469,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.317613830526013</v>
+        <v>1.380952390545853</v>
       </c>
       <c r="E2" t="n">
-        <v>1.189075385134696e-15</v>
+        <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.781162872455906</v>
+        <v>1.855012479325758</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.219880128675453</v>
+        <v>1.235871947074367</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -547,10 +547,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.443499789305178</v>
+        <v>1.5154593997107</v>
       </c>
       <c r="E5" t="n">
-        <v>1.326365873357462e-15</v>
+        <v>0</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -573,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.938485118341074</v>
+        <v>2.023921338867937</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1632052780676055</v>
+        <v>0.2036727269423182</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -625,10 +625,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.36091605868904</v>
+        <v>1.495014618324038</v>
       </c>
       <c r="E8" t="n">
-        <v>2.256916269211037e-15</v>
+        <v>0</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.31662597947677</v>
+        <v>1.436373553856646</v>
       </c>
       <c r="E9" t="n">
-        <v>7.665380815945723e-16</v>
+        <v>0</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -677,10 +677,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.931287334905569</v>
+        <v>2.016511458028876</v>
       </c>
       <c r="E10" t="n">
-        <v>1.194044364190914e-15</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -703,10 +703,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.750042317949569</v>
+        <v>1.82782416710573</v>
       </c>
       <c r="E11" t="n">
-        <v>6.812384756742752e-16</v>
+        <v>0</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.80432654648811</v>
+        <v>1.886704229778474</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -755,10 +755,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.088694071602357</v>
+        <v>1.238226358321845</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2.832679630003802e-15</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -781,10 +781,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.520817460428739</v>
+        <v>1.634254142862045</v>
       </c>
       <c r="E14" t="n">
-        <v>9.710423282478615e-16</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -807,10 +807,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.270155915444457</v>
+        <v>1.293427054000308</v>
       </c>
       <c r="E15" t="n">
-        <v>1.407826725960803e-15</v>
+        <v>0</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.741390373791625</v>
+        <v>1.829861446665436</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.888971218270645</v>
+        <v>1.984384528815371</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.628640649575243</v>
+        <v>1.738975538242739</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.940366918067935</v>
+        <v>2.02925021560261</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.318041862977727</v>
+        <v>1.391583495543818</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.536401201940057</v>
+        <v>1.658102873304567</v>
       </c>
       <c r="E21" t="n">
-        <v>2.606595123082029e-16</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -989,10 +989,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.339201520218406</v>
+        <v>1.404080060281603</v>
       </c>
       <c r="E22" t="n">
-        <v>9.404000643479899e-16</v>
+        <v>0</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.808939287200494</v>
+        <v>1.912527286377071</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1041,10 +1041,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.059190013324527</v>
+        <v>1.071694727360966</v>
       </c>
       <c r="E24" t="n">
-        <v>1.328858020699466e-13</v>
+        <v>2.362452798588172e-13</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.101466059610553</v>
+        <v>1.157171333784546</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1093,10 +1093,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.37988518413797</v>
+        <v>1.453675173355385</v>
       </c>
       <c r="E26" t="n">
-        <v>9.21707741267982e-16</v>
+        <v>0</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.901948423452025</v>
+        <v>1.992482091225681</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.708926746158336</v>
+        <v>1.798877564063546</v>
       </c>
       <c r="E28" t="n">
-        <v>7.412592303167149e-16</v>
+        <v>0</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1.944659849381832</v>
+        <v>2.031567010435596</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1.918571780518689</v>
+        <v>2.010846494565024</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1.490098968339053</v>
+        <v>1.527846921251021</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1.37286717702204</v>
+        <v>1.442895854323849</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1275,13 +1275,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1.000426341459924</v>
+        <v>1.130013950024312</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03295124996975603</v>
+        <v>2.096052345226416e-15</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -1301,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1.851872747873966</v>
+        <v>1.920974338796864</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1327,10 +1327,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1.80574470427728</v>
+        <v>1.887136564650478</v>
       </c>
       <c r="E35" t="n">
-        <v>1.525814963703432e-16</v>
+        <v>0</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1.753488884214829</v>
+        <v>1.8278895752071</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1.915637400603278</v>
+        <v>1.998140340965494</v>
       </c>
       <c r="E37" t="n">
-        <v>4.734080768907847e-17</v>
+        <v>0</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1.931161980401739</v>
+        <v>2.015083425683318</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1431,10 +1431,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1.709621399562232</v>
+        <v>1.823465616916882</v>
       </c>
       <c r="E39" t="n">
-        <v>3.032273861717596e-17</v>
+        <v>0</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1.894512639558282</v>
+        <v>1.978910863517936</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1483,10 +1483,10 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1.490365430468519</v>
+        <v>1.618283292192319</v>
       </c>
       <c r="E41" t="n">
-        <v>1.214073021474065e-15</v>
+        <v>0</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1.753249066626529</v>
+        <v>1.832184133869068</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1535,10 +1535,10 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1.232298601848307</v>
+        <v>1.279434755151591</v>
       </c>
       <c r="E43" t="n">
-        <v>2.786233870535721e-16</v>
+        <v>0</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1.447135896549416</v>
+        <v>1.57485381281108</v>
       </c>
       <c r="E44" t="n">
-        <v>9.99502635275606e-16</v>
+        <v>0</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1.837237709707363</v>
+        <v>1.936930700204741</v>
       </c>
       <c r="E45" t="n">
-        <v>3.564033182557694e-16</v>
+        <v>0</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1.213556068658695</v>
+        <v>1.291360312227316</v>
       </c>
       <c r="E46" t="n">
-        <v>1.46668535139961e-15</v>
+        <v>0</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -1639,10 +1639,10 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1.27810609912797</v>
+        <v>1.365522507575758</v>
       </c>
       <c r="E47" t="n">
-        <v>1.672521070167877e-16</v>
+        <v>0</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -1665,10 +1665,10 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1.781780206017508</v>
+        <v>1.881716220162115</v>
       </c>
       <c r="E48" t="n">
-        <v>6.210773973502152e-16</v>
+        <v>0</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -1691,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1.871341809369542</v>
+        <v>1.951686193629636</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1717,10 +1717,10 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1.487361307705705</v>
+        <v>1.559295177020455</v>
       </c>
       <c r="E50" t="n">
-        <v>8.068060279070417e-16</v>
+        <v>0</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1.934824341102773</v>
+        <v>2.015470027040585</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>-1</v>
       </c>
       <c r="D52" t="n">
-        <v>-4.601350294285004</v>
+        <v>-4.925316935615741</v>
       </c>
       <c r="E52" t="n">
-        <v>1.361843672831047e-15</v>
+        <v>0</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -1795,10 +1795,10 @@
         <v>-1</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.345227484642354</v>
+        <v>-3.427007190953731</v>
       </c>
       <c r="E53" t="n">
-        <v>2.6084918017945e-15</v>
+        <v>0</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -1821,10 +1821,10 @@
         <v>-1</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.849240870830686</v>
+        <v>-1.857980612961537</v>
       </c>
       <c r="E54" t="n">
-        <v>8.949374369135779e-17</v>
+        <v>5.987691290189725e-15</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         <v>-1</v>
       </c>
       <c r="D55" t="n">
-        <v>-4.910168464166189</v>
+        <v>-4.591649929286107</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>-1</v>
       </c>
       <c r="D56" t="n">
-        <v>-4.016750484532709</v>
+        <v>-3.993954752554487</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>-1</v>
       </c>
       <c r="D57" t="n">
-        <v>-3.927225558143323</v>
+        <v>-4.054352561490018</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>9.301224725944856e-16</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -1925,10 +1925,10 @@
         <v>-1</v>
       </c>
       <c r="D58" t="n">
-        <v>-2.711014331565236</v>
+        <v>-2.827310020511473</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1.530974288438303e-14</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>-1</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.931487056577667</v>
+        <v>-1.95371718134526</v>
       </c>
       <c r="E59" t="n">
-        <v>6.926320877913608e-17</v>
+        <v>9.411201951347844e-15</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -1977,10 +1977,10 @@
         <v>-1</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.257240271110807</v>
+        <v>-1.379811125350551</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>2.261104491697069e-14</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         <v>-1</v>
       </c>
       <c r="D61" t="n">
-        <v>-4.785985773665034</v>
+        <v>-5.17454992227053</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>6.677325187053442e-15</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-1</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.537596167498387</v>
+        <v>-2.502816919643328</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2055,10 +2055,10 @@
         <v>-1</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.30751667581212</v>
+        <v>-1.308459464953103</v>
       </c>
       <c r="E63" t="n">
-        <v>7.329782299022401e-15</v>
+        <v>0</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>-1</v>
       </c>
       <c r="D64" t="n">
-        <v>-2.132956952586</v>
+        <v>-2.240937203508163</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1.974288293735038e-14</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="D65" t="n">
-        <v>-2.845827604608017</v>
+        <v>-2.714506216924538</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>-1</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.426448933557224</v>
+        <v>-1.209245622524496</v>
       </c>
       <c r="E66" t="n">
-        <v>5.108472947424435e-14</v>
+        <v>2.284413483152792e-14</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="D67" t="n">
-        <v>-4.394234409822037</v>
+        <v>-4.344135181127046</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2185,10 +2185,10 @@
         <v>-1</v>
       </c>
       <c r="D68" t="n">
-        <v>-3.841680492489044</v>
+        <v>-4.11740377252482</v>
       </c>
       <c r="E68" t="n">
-        <v>1.99216013618617e-15</v>
+        <v>0</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -2211,10 +2211,10 @@
         <v>-1</v>
       </c>
       <c r="D69" t="n">
-        <v>-3.732414451028758</v>
+        <v>-4.035919969222589</v>
       </c>
       <c r="E69" t="n">
-        <v>3.017059901646612e-16</v>
+        <v>4.255515689318259e-15</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -2237,10 +2237,10 @@
         <v>-1</v>
       </c>
       <c r="D70" t="n">
-        <v>-2.573618606949389</v>
+        <v>-2.62705166292892</v>
       </c>
       <c r="E70" t="n">
-        <v>1.234611751545257e-16</v>
+        <v>7.953017791990621e-15</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -2263,10 +2263,10 @@
         <v>-1</v>
       </c>
       <c r="D71" t="n">
-        <v>-2.940643216811957</v>
+        <v>-2.871813417620951</v>
       </c>
       <c r="E71" t="n">
-        <v>7.801711851460923e-16</v>
+        <v>0</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -2289,10 +2289,10 @@
         <v>-1</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.301856388390052</v>
+        <v>-3.434903758900436</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1.15866874917579e-14</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>-1</v>
       </c>
       <c r="D73" t="n">
-        <v>-3.285617510511187</v>
+        <v>-2.95563431154138</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>-1</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.268615860295661</v>
+        <v>-1.32812660559181</v>
       </c>
       <c r="E74" t="n">
-        <v>3.670413619635427e-15</v>
+        <v>2.137062954022076e-14</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>-1</v>
       </c>
       <c r="D75" t="n">
-        <v>-2.081320488455639</v>
+        <v>-2.049611152200865</v>
       </c>
       <c r="E75" t="n">
-        <v>3.920610211595402e-15</v>
+        <v>0</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -2393,10 +2393,10 @@
         <v>-1</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.059020741806382</v>
+        <v>-1.074972823201657</v>
       </c>
       <c r="E76" t="n">
-        <v>1.845213472364704e-15</v>
+        <v>2.523335727771633e-14</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>-1</v>
       </c>
       <c r="D77" t="n">
-        <v>-2.505714065227803</v>
+        <v>-2.385152311259739</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>-1</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.945772517788506</v>
+        <v>-1.722013855695984</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2471,13 +2471,13 @@
         <v>-1</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.095044403161621</v>
+        <v>-0.9992878929511355</v>
       </c>
       <c r="E79" t="n">
-        <v>5.125397004523755e-14</v>
+        <v>0.02957386344288537</v>
       </c>
       <c r="F79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
         <v>-1</v>
@@ -2497,13 +2497,13 @@
         <v>-1</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.9995891315847787</v>
+        <v>-1.03587170198293</v>
       </c>
       <c r="E80" t="n">
-        <v>0.06973627732938958</v>
+        <v>2.394106253209596e-13</v>
       </c>
       <c r="F80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>-1</v>
@@ -2523,10 +2523,10 @@
         <v>-1</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.270750795503477</v>
+        <v>-3.545661822535961</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1.620950193853801e-14</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -2549,10 +2549,10 @@
         <v>-1</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.232317678129286</v>
+        <v>-1.276376736086799</v>
       </c>
       <c r="E82" t="n">
-        <v>5.756442316420061e-15</v>
+        <v>0</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>-1</v>
       </c>
       <c r="D83" t="n">
-        <v>-4.421782365739423</v>
+        <v>-4.535176289985293</v>
       </c>
       <c r="E83" t="n">
-        <v>2.633277396109431e-15</v>
+        <v>0</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>-1</v>
       </c>
       <c r="D84" t="n">
-        <v>-2.987392828497327</v>
+        <v>-2.671502880955617</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -2627,10 +2627,10 @@
         <v>-1</v>
       </c>
       <c r="D85" t="n">
-        <v>-2.21932270290672</v>
+        <v>-2.26075780752018</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1.019381296076577e-14</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -2653,10 +2653,10 @@
         <v>-1</v>
       </c>
       <c r="D86" t="n">
-        <v>-3.235810311608228</v>
+        <v>-3.524070237392632</v>
       </c>
       <c r="E86" t="n">
-        <v>2.012007812206232e-15</v>
+        <v>1.466233188587404e-14</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -2679,10 +2679,10 @@
         <v>-1</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.9998677123452608</v>
+        <v>-0.9995181764730443</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08459215025071107</v>
+        <v>0.06267955737837866</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -2705,7 +2705,7 @@
         <v>-1</v>
       </c>
       <c r="D88" t="n">
-        <v>-4.902769165171716</v>
+        <v>-4.849400092195957</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -2731,7 +2731,7 @@
         <v>-1</v>
       </c>
       <c r="D89" t="n">
-        <v>-2.608167330205244</v>
+        <v>-2.550414479877448</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>-1</v>
       </c>
       <c r="D90" t="n">
-        <v>-4.221300284697905</v>
+        <v>-4.554738745937142</v>
       </c>
       <c r="E90" t="n">
-        <v>1.301538641553077e-15</v>
+        <v>1.25602332800141e-14</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
@@ -2783,10 +2783,10 @@
         <v>-1</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.259370376520873</v>
+        <v>-1.315516451041811</v>
       </c>
       <c r="E91" t="n">
-        <v>3.64796047026961e-15</v>
+        <v>2.308806676781e-14</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -2809,10 +2809,10 @@
         <v>-1</v>
       </c>
       <c r="D92" t="n">
-        <v>-2.362929823032369</v>
+        <v>-2.329862325016857</v>
       </c>
       <c r="E92" t="n">
-        <v>3.708648686874486e-15</v>
+        <v>0</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -2835,10 +2835,10 @@
         <v>-1</v>
       </c>
       <c r="D93" t="n">
-        <v>-2.928820591078613</v>
+        <v>-3.080010383318558</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1.730863221968593e-14</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>-1</v>
       </c>
       <c r="D94" t="n">
-        <v>-4.884138698260722</v>
+        <v>-4.908855133077981</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -2887,10 +2887,10 @@
         <v>-1</v>
       </c>
       <c r="D95" t="n">
-        <v>-2.973081848210232</v>
+        <v>-3.199666966629109</v>
       </c>
       <c r="E95" t="n">
-        <v>5.037833116496668e-15</v>
+        <v>1.258180693828277e-15</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -2913,10 +2913,10 @@
         <v>-1</v>
       </c>
       <c r="D96" t="n">
-        <v>-2.745430681439903</v>
+        <v>-2.798270336330949</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>2.412256799612075e-15</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -2939,10 +2939,10 @@
         <v>-1</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.930064774400585</v>
+        <v>-1.992977012376451</v>
       </c>
       <c r="E97" t="n">
-        <v>1.946579662906627e-16</v>
+        <v>1.295064092979898e-14</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
@@ -2965,7 +2965,7 @@
         <v>-1</v>
       </c>
       <c r="D98" t="n">
-        <v>-2.088390524680883</v>
+        <v>-1.951033191382248</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -2991,10 +2991,10 @@
         <v>-1</v>
       </c>
       <c r="D99" t="n">
-        <v>-2.620257701552271</v>
+        <v>-2.740046392816992</v>
       </c>
       <c r="E99" t="n">
-        <v>3.190660934574169e-15</v>
+        <v>0</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
@@ -3017,10 +3017,10 @@
         <v>-1</v>
       </c>
       <c r="D100" t="n">
-        <v>-2.675647581486523</v>
+        <v>-2.789012304051694</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1.320132202460478e-14</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
@@ -3043,10 +3043,10 @@
         <v>-1</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.9992806337873212</v>
+        <v>-0.9997534679246693</v>
       </c>
       <c r="E101" t="n">
-        <v>0.04182810045730472</v>
+        <v>0.1114193061210356</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
